--- a/10_AI_research/04_creating_output/AI_Research_Technical_Outputs.xlsx
+++ b/10_AI_research/04_creating_output/AI_Research_Technical_Outputs.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Occupation_Master'!$A$1:$L$538</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Archetype_Comparison'!$A$1:$J$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sector_Comparison'!$A$1:$L$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Six_Occupations'!$A$1:$N$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Six_Occupations'!$A$1:$N$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Checks'!$A$1:$E$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,9 +455,9 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
@@ -492,17 +492,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Archetype C-AIOE Percentile 50</t>
+          <t>Archetype C-AIOE Percentile - Observed Exposure 50</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Archetype C-AIOE Percentile 60</t>
+          <t>Archetype C-AIOE Percentile - Observed Exposure 60</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Archetype C-AIOE Percentile 75</t>
+          <t>Archetype C-AIOE Percentile - Observed Exposure 75</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -550,17 +550,17 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
@@ -942,17 +942,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
@@ -998,17 +998,17 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
@@ -1110,17 +1110,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
@@ -1222,17 +1222,17 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
@@ -1278,17 +1278,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
@@ -1670,17 +1670,17 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
@@ -2062,17 +2062,17 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
@@ -2286,17 +2286,17 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
@@ -2398,17 +2398,17 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
@@ -2454,17 +2454,17 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
@@ -2510,17 +2510,17 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
@@ -2622,17 +2622,17 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
@@ -2678,17 +2678,17 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Active Transformation</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Active Transformation</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Active Transformation</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
@@ -2734,17 +2734,17 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
@@ -2902,17 +2902,17 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
@@ -3070,17 +3070,17 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
@@ -3126,17 +3126,17 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
@@ -3350,17 +3350,17 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
@@ -3630,17 +3630,17 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
@@ -3798,17 +3798,17 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
@@ -3854,17 +3854,17 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
@@ -4022,17 +4022,17 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
@@ -4078,17 +4078,17 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
@@ -4134,17 +4134,17 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
@@ -4190,17 +4190,17 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
@@ -4358,17 +4358,17 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
@@ -4526,17 +4526,17 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
@@ -4582,17 +4582,17 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
@@ -4638,17 +4638,17 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
@@ -4694,17 +4694,17 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
@@ -4862,17 +4862,17 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
@@ -4918,17 +4918,17 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
@@ -5030,17 +5030,17 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
@@ -5086,17 +5086,17 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
@@ -5142,17 +5142,17 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
@@ -5422,17 +5422,17 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
@@ -5534,17 +5534,17 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
@@ -5758,17 +5758,17 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
@@ -5870,17 +5870,17 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
@@ -6038,17 +6038,17 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
@@ -6094,17 +6094,17 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
@@ -6542,17 +6542,17 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
@@ -6710,17 +6710,17 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Active Transformation</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Active Transformation</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Active Transformation</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
@@ -7102,17 +7102,17 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
@@ -7326,17 +7326,17 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
@@ -7998,17 +7998,17 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Active Transformation</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Active Transformation</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I135" s="2" t="n">
@@ -8334,17 +8334,17 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Active Transformation</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Active Transformation</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Active Transformation</t>
         </is>
       </c>
       <c r="I141" s="2" t="n">
@@ -9622,17 +9622,17 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
@@ -9734,17 +9734,17 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
@@ -10182,17 +10182,17 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Active Transformation</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Active Transformation</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Active Transformation</t>
         </is>
       </c>
       <c r="I174" s="2" t="n">
@@ -10630,17 +10630,17 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Active Transformation</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I182" s="2" t="n">
@@ -10742,17 +10742,17 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I184" s="2" t="n">
@@ -11302,17 +11302,17 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I194" s="2" t="n">
@@ -11694,17 +11694,17 @@
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I201" s="2" t="n">
@@ -12310,17 +12310,17 @@
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I212" s="2" t="n">
@@ -12926,17 +12926,17 @@
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I223" s="2" t="n">
@@ -13150,17 +13150,17 @@
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I227" s="2" t="n">
@@ -13990,17 +13990,17 @@
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I242" s="2" t="n">
@@ -14438,17 +14438,17 @@
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I250" s="2" t="n">
@@ -14662,17 +14662,17 @@
       </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I254" s="2" t="n">
@@ -14998,17 +14998,17 @@
       </c>
       <c r="F260" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I260" s="2" t="n">
@@ -15110,17 +15110,17 @@
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I262" s="2" t="n">
@@ -15166,17 +15166,17 @@
       </c>
       <c r="F263" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I263" s="2" t="n">
@@ -15558,17 +15558,17 @@
       </c>
       <c r="F270" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I270" s="2" t="n">
@@ -15726,17 +15726,17 @@
       </c>
       <c r="F273" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I273" s="2" t="n">
@@ -16230,17 +16230,17 @@
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I282" s="2" t="n">
@@ -17182,17 +17182,17 @@
       </c>
       <c r="F299" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Active Transformation</t>
         </is>
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Active Transformation</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I299" s="2" t="n">
@@ -17294,17 +17294,17 @@
       </c>
       <c r="F301" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I301" s="2" t="n">
@@ -17686,17 +17686,17 @@
       </c>
       <c r="F308" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="I308" s="2" t="n">
@@ -17798,17 +17798,17 @@
       </c>
       <c r="F310" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I310" s="2" t="n">
@@ -18694,17 +18694,17 @@
       </c>
       <c r="F326" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I326" s="2" t="n">
@@ -18862,17 +18862,17 @@
       </c>
       <c r="F329" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Active Transformation</t>
         </is>
       </c>
       <c r="G329" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Active Transformation</t>
         </is>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Active Transformation</t>
         </is>
       </c>
       <c r="I329" s="2" t="n">
@@ -19030,17 +19030,17 @@
       </c>
       <c r="F332" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="G332" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I332" s="2" t="n">
@@ -19814,17 +19814,17 @@
       </c>
       <c r="F346" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Active Transformation</t>
         </is>
       </c>
       <c r="G346" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Active Transformation</t>
         </is>
       </c>
       <c r="H346" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I346" s="2" t="n">
@@ -20430,17 +20430,17 @@
       </c>
       <c r="F357" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G357" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H357" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I357" s="2" t="n">
@@ -20598,17 +20598,17 @@
       </c>
       <c r="F360" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="G360" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="H360" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I360" s="2" t="n">
@@ -20934,17 +20934,17 @@
       </c>
       <c r="F366" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="G366" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="H366" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="I366" s="2" t="n">
@@ -21158,17 +21158,17 @@
       </c>
       <c r="F370" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G370" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H370" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I370" s="2" t="n">
@@ -21270,17 +21270,17 @@
       </c>
       <c r="F372" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H372" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I372" s="2" t="n">
@@ -21326,17 +21326,17 @@
       </c>
       <c r="F373" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G373" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H373" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I373" s="2" t="n">
@@ -21550,17 +21550,17 @@
       </c>
       <c r="F377" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="G377" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H377" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I377" s="2" t="n">
@@ -21718,17 +21718,17 @@
       </c>
       <c r="F380" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G380" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H380" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I380" s="2" t="n">
@@ -22278,17 +22278,17 @@
       </c>
       <c r="F390" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G390" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H390" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I390" s="2" t="n">
@@ -22726,17 +22726,17 @@
       </c>
       <c r="F398" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G398" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H398" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I398" s="2" t="n">
@@ -22838,17 +22838,17 @@
       </c>
       <c r="F400" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G400" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H400" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I400" s="2" t="n">
@@ -22950,17 +22950,17 @@
       </c>
       <c r="F402" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="G402" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H402" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I402" s="2" t="n">
@@ -23062,17 +23062,17 @@
       </c>
       <c r="F404" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G404" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H404" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I404" s="2" t="n">
@@ -23118,17 +23118,17 @@
       </c>
       <c r="F405" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G405" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H405" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I405" s="2" t="n">
@@ -23174,17 +23174,17 @@
       </c>
       <c r="F406" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G406" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H406" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I406" s="2" t="n">
@@ -23230,17 +23230,17 @@
       </c>
       <c r="F407" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G407" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H407" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I407" s="2" t="n">
@@ -23342,17 +23342,17 @@
       </c>
       <c r="F409" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I409" s="2" t="n">
@@ -23622,17 +23622,17 @@
       </c>
       <c r="F414" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
         <is>
-          <t>Limited Current Transformation</t>
+          <t>Latent Transformation</t>
         </is>
       </c>
       <c r="I414" s="2" t="n">
@@ -23734,17 +23734,17 @@
       </c>
       <c r="F416" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I416" s="2" t="n">
@@ -23790,17 +23790,17 @@
       </c>
       <c r="F417" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I417" s="2" t="n">
@@ -23846,17 +23846,17 @@
       </c>
       <c r="F418" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I418" s="2" t="n">
@@ -23902,17 +23902,17 @@
       </c>
       <c r="F419" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G419" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H419" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I419" s="2" t="n">
@@ -23958,17 +23958,17 @@
       </c>
       <c r="F420" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I420" s="2" t="n">
@@ -24014,17 +24014,17 @@
       </c>
       <c r="F421" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G421" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H421" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I421" s="2" t="n">
@@ -24126,17 +24126,17 @@
       </c>
       <c r="F423" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G423" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H423" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I423" s="2" t="n">
@@ -24182,17 +24182,17 @@
       </c>
       <c r="F424" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G424" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H424" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I424" s="2" t="n">
@@ -24294,17 +24294,17 @@
       </c>
       <c r="F426" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G426" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H426" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I426" s="2" t="n">
@@ -24630,17 +24630,17 @@
       </c>
       <c r="F432" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G432" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H432" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I432" s="2" t="n">
@@ -24686,17 +24686,17 @@
       </c>
       <c r="F433" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G433" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H433" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I433" s="2" t="n">
@@ -24910,17 +24910,17 @@
       </c>
       <c r="F437" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G437" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H437" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I437" s="2" t="n">
@@ -24966,17 +24966,17 @@
       </c>
       <c r="F438" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G438" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H438" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I438" s="2" t="n">
@@ -25246,17 +25246,17 @@
       </c>
       <c r="F443" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G443" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H443" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I443" s="2" t="n">
@@ -25414,17 +25414,17 @@
       </c>
       <c r="F446" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="G446" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H446" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I446" s="2" t="n">
@@ -25526,17 +25526,17 @@
       </c>
       <c r="F448" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G448" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H448" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I448" s="2" t="n">
@@ -25694,17 +25694,17 @@
       </c>
       <c r="F451" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G451" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H451" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I451" s="2" t="n">
@@ -25862,17 +25862,17 @@
       </c>
       <c r="F454" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G454" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H454" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I454" s="2" t="n">
@@ -25918,17 +25918,17 @@
       </c>
       <c r="F455" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I455" s="2" t="n">
@@ -26030,17 +26030,17 @@
       </c>
       <c r="F457" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I457" s="2" t="n">
@@ -26086,17 +26086,17 @@
       </c>
       <c r="F458" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I458" s="2" t="n">
@@ -26198,17 +26198,17 @@
       </c>
       <c r="F460" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="I460" s="2" t="n">
@@ -26310,17 +26310,17 @@
       </c>
       <c r="F462" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I462" s="2" t="n">
@@ -26366,17 +26366,17 @@
       </c>
       <c r="F463" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I463" s="2" t="n">
@@ -26478,17 +26478,17 @@
       </c>
       <c r="F465" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I465" s="2" t="n">
@@ -26534,17 +26534,17 @@
       </c>
       <c r="F466" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G466" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H466" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I466" s="2" t="n">
@@ -26702,17 +26702,17 @@
       </c>
       <c r="F469" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="G469" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="H469" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="I469" s="2" t="n">
@@ -26814,17 +26814,17 @@
       </c>
       <c r="F471" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G471" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H471" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I471" s="2" t="n">
@@ -27038,17 +27038,17 @@
       </c>
       <c r="F475" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G475" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H475" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I475" s="2" t="n">
@@ -27206,17 +27206,17 @@
       </c>
       <c r="F478" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="G478" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="H478" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I478" s="2" t="n">
@@ -27318,17 +27318,17 @@
       </c>
       <c r="F480" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G480" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H480" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I480" s="2" t="n">
@@ -27374,17 +27374,17 @@
       </c>
       <c r="F481" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="G481" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="H481" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I481" s="2" t="n">
@@ -27766,17 +27766,17 @@
       </c>
       <c r="F488" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I488" s="2" t="n">
@@ -27822,17 +27822,17 @@
       </c>
       <c r="F489" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I489" s="2" t="n">
@@ -28102,17 +28102,17 @@
       </c>
       <c r="F494" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="G494" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H494" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I494" s="2" t="n">
@@ -28270,17 +28270,17 @@
       </c>
       <c r="F497" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="G497" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="H497" s="2" t="inlineStr">
         <is>
-          <t>Active Transformation</t>
+          <t>AI-Enabled Expansion</t>
         </is>
       </c>
       <c r="I497" s="2" t="n">
@@ -28326,17 +28326,17 @@
       </c>
       <c r="F498" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G498" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H498" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I498" s="2" t="n">
@@ -28550,17 +28550,17 @@
       </c>
       <c r="F502" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G502" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H502" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I502" s="2" t="n">
@@ -28718,17 +28718,17 @@
       </c>
       <c r="F505" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G505" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H505" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I505" s="2" t="n">
@@ -28998,17 +28998,17 @@
       </c>
       <c r="F510" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G510" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H510" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I510" s="2" t="n">
@@ -29110,17 +29110,17 @@
       </c>
       <c r="F512" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G512" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H512" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I512" s="2" t="n">
@@ -29278,17 +29278,17 @@
       </c>
       <c r="F515" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I515" s="2" t="n">
@@ -29670,17 +29670,17 @@
       </c>
       <c r="F522" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I522" s="2" t="n">
@@ -30510,17 +30510,17 @@
       </c>
       <c r="F537" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G537" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H537" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I537" s="2" t="n">
@@ -30566,17 +30566,17 @@
       </c>
       <c r="F538" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="G538" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="H538" s="2" t="inlineStr">
         <is>
-          <t>Latent Transformation</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="I538" s="2" t="n">
@@ -30622,7 +30622,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -30687,28 +30687,28 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3.538175046554934</v>
+        <v>5.772811918063315</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>3.755868544600939</v>
+        <v>4.694835680751173</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>4.263565891472868</v>
+        <v>5.038759689922481</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.2176934980460046</v>
+        <v>-1.077976237312142</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.7253908449179334</v>
+        <v>-0.7340522281408344</v>
       </c>
     </row>
     <row r="3">
@@ -30721,28 +30721,28 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>25.88454376163874</v>
+        <v>23.64990689013035</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>37.79342723004695</v>
+        <v>36.85446009389671</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>29.84496124031007</v>
+        <v>29.06976744186047</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>11.90888346840822</v>
+        <v>13.20455320376636</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.960417478671339</v>
+        <v>5.419860551730114</v>
       </c>
     </row>
     <row r="4">
@@ -30755,28 +30755,28 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>24.02234636871508</v>
+        <v>26.44320297951583</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>15.61032863849765</v>
+        <v>18.07511737089202</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>17.05426356589147</v>
+        <v>23.64341085271318</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-8.41201773021743</v>
+        <v>-8.368085608623808</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-6.968082802823613</v>
+        <v>-2.79979212680265</v>
       </c>
     </row>
     <row r="5">
@@ -30789,28 +30789,28 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>46.55493482309125</v>
+        <v>44.1340782122905</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>365</v>
+        <v>344</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>42.84037558685446</v>
+        <v>40.3755868544601</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>48.83720930232558</v>
+        <v>42.24806201550388</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-3.714559236236788</v>
+        <v>-3.758491357830408</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.282274479234324</v>
+        <v>-1.886016196786628</v>
       </c>
     </row>
     <row r="6">
@@ -30823,16 +30823,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2.420856610800745</v>
+        <v>3.538175046554934</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>3.403755868544601</v>
+        <v>3.873239436619718</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>8</v>
@@ -30841,10 +30841,10 @@
         <v>3.10077519379845</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9828992577438562</v>
+        <v>0.3350643900647836</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.679918582997705</v>
+        <v>-0.4373998527564846</v>
       </c>
     </row>
     <row r="7">
@@ -30857,16 +30857,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>21.22905027932961</v>
+        <v>20.11173184357542</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>35.44600938967136</v>
+        <v>34.97652582159624</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>66</v>
@@ -30875,10 +30875,10 @@
         <v>25.58139534883721</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>14.21695911034175</v>
+        <v>14.86479397802082</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>4.352345069507603</v>
+        <v>5.469663505261792</v>
       </c>
     </row>
     <row r="8">
@@ -30891,28 +30891,28 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>28.67783985102421</v>
+        <v>29.98137802607076</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>17.95774647887324</v>
+        <v>19.95305164319249</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>21.31782945736434</v>
+        <v>27.13178294573643</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-10.72009337215097</v>
+        <v>-10.02832638287828</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-7.360010393659866</v>
+        <v>-2.849595080334332</v>
       </c>
     </row>
     <row r="9">
@@ -30925,28 +30925,28 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>47.67225325884544</v>
+        <v>46.36871508379888</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>43.1924882629108</v>
+        <v>41.19718309859155</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>50</v>
+        <v>44.18604651162791</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-4.479764995934637</v>
+        <v>-5.171531985207331</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.327746741154563</v>
+        <v>-2.182668572170975</v>
       </c>
     </row>
     <row r="10">
@@ -30965,10 +30965,10 @@
         <v>1.48975791433892</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2.934272300469484</v>
+        <v>3.286384976525822</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>5</v>
@@ -30977,7 +30977,7 @@
         <v>1.937984496124031</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1.444514386130564</v>
+        <v>1.796627062186902</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>0.448226581785111</v>
@@ -30999,10 +30999,10 @@
         <v>13.22160148975791</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>24.88262910798122</v>
+        <v>24.53051643192488</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>48</v>
@@ -31011,7 +31011,7 @@
         <v>18.6046511627907</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>11.66102761822331</v>
+        <v>11.30891494216697</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>5.383049673032785</v>
@@ -31027,28 +31027,28 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>36.6852886405959</v>
+        <v>36.87150837988827</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>28.52112676056338</v>
+        <v>30.39906103286385</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>28.29457364341085</v>
+        <v>34.10852713178294</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-8.16416188003252</v>
+        <v>-6.472447347024421</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-8.390714997185047</v>
+        <v>-2.762981248105326</v>
       </c>
     </row>
     <row r="13">
@@ -31061,28 +31061,28 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>48.60335195530726</v>
+        <v>48.4171322160149</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>43.66197183098591</v>
+        <v>41.78403755868544</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>51.16279069767442</v>
+        <v>45.34883720930232</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-4.941380124321348</v>
+        <v>-6.633094657329458</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.559438742367163</v>
+        <v>-3.068295006712574</v>
       </c>
     </row>
   </sheetData>
@@ -31186,74 +31186,74 @@
         <v>47</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>57.44680851063831</v>
+        <v>59.57446808510638</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>96</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>79.16666666666666</v>
+        <v>88.54166666666666</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>25</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>10.55319148936169</v>
+        <v>12.42553191489362</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>23.60248447204969</v>
+        <v>27.07006369426751</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Computer and Mathematical</t>
+          <t>Arts, Design, Entertainment, Sports, and Media</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>94.73684210526315</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>98.46153846153847</v>
+        <v>55.33980582524271</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>92.85714285714286</v>
+        <v>38.46153846153847</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-1.879699248120289</v>
+        <v>2.0979020979021</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>19.87577639751553</v>
+        <v>18.15286624203821</v>
       </c>
     </row>
     <row r="4">
@@ -31293,47 +31293,47 @@
         <v>22.72727272727273</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>17.39130434782609</v>
+        <v>17.8343949044586</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Arts, Design, Entertainment, Sports, and Media</t>
+          <t>Computer and Mathematical</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>33.33333333333333</v>
+        <v>89.47368421052632</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>50</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>48.54368932038835</v>
+        <v>76.92307692307693</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>34.61538461538461</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1.282051282051285</v>
+        <v>-3.759398496240607</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>15.527950310559</v>
+        <v>15.92356687898089</v>
       </c>
     </row>
     <row r="6">
@@ -31346,34 +31346,34 @@
         <v>56</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>35.71428571428572</v>
+        <v>23.21428571428572</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>65</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>43.07692307692308</v>
+        <v>29.23076923076923</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>20</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>9.285714285714285</v>
+        <v>6.785714285714285</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>8.695652173913043</v>
+        <v>6.050955414012739</v>
       </c>
     </row>
     <row r="7">
@@ -31395,25 +31395,25 @@
         <v>76</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>21.05263157894737</v>
+        <v>22.36842105263158</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>24</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-5.043859649122805</v>
+        <v>-0.877192982456144</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>4.968944099378882</v>
+        <v>5.414012738853503</v>
       </c>
     </row>
     <row r="8">
@@ -31426,10 +31426,10 @@
         <v>18</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>77.77777777777779</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>17</v>
@@ -31450,10 +31450,10 @@
         <v>66.66666666666666</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-11.11111111111113</v>
+        <v>-5.555555555555557</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>4.037267080745342</v>
+        <v>4.140127388535031</v>
       </c>
     </row>
     <row r="9">
@@ -31466,34 +31466,34 @@
         <v>50</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>42</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>26.19047619047619</v>
+        <v>23.80952380952381</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>18</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>16.66666666666666</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>6.666666666666664</v>
+        <v>7.111111111111111</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>3.416149068322981</v>
+        <v>3.184713375796179</v>
       </c>
     </row>
     <row r="10">
@@ -31506,74 +31506,74 @@
         <v>7</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>42.85714285714285</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>100</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>57.14285714285715</v>
+        <v>9.523809523809518</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1.552795031055901</v>
+        <v>1.273885350318471</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Architecture and Engineering</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>33.33333333333333</v>
+        <v>6.451612903225806</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>50</v>
+        <v>1.639344262295082</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>50</v>
+        <v>5.88235294117647</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>16.66666666666667</v>
+        <v>-0.5692599620493359</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0.6211180124223602</v>
+        <v>0.3184713375796179</v>
       </c>
     </row>
     <row r="12">
@@ -31586,10 +31586,10 @@
         <v>12</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>16.66666666666666</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>33</v>
@@ -31610,50 +31610,50 @@
         <v>16.66666666666666</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0.3105590062111801</v>
+        <v>0.3184713375796179</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Architecture and Engineering</t>
+          <t>Healthcare Support</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>3.225806451612903</v>
+        <v>9.090909090909092</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0</v>
+        <v>3.571428571428571</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>-3.225806451612903</v>
+        <v>5.194805194805193</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>0.3184713375796179</v>
       </c>
     </row>
     <row r="14">
@@ -31819,11 +31819,11 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Healthcare Support</t>
+          <t>Installation, Maintenance, and Repair</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>0</v>
@@ -31832,7 +31832,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
@@ -31841,7 +31841,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I18" s="2" t="n">
         <v>0</v>
@@ -31859,20 +31859,20 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Installation, Maintenance, and Repair</t>
+          <t>Management</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>21.21212121212121</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>0</v>
@@ -31881,7 +31881,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I19" s="2" t="n">
         <v>0</v>
@@ -31890,7 +31890,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>-21.21212121212121</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -32068,7 +32068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32078,9 +32078,9 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="25" customWidth="1" min="13" max="13"/>
@@ -32125,17 +32125,17 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Archetype_C-AIOE_Percentile_50</t>
+          <t>Archetype_C-AIOE_Percentile_-_Observed_Exposure_50</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Archetype_C-AIOE_Percentile_60</t>
+          <t>Archetype_C-AIOE_Percentile_-_Observed_Exposure_60</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Archetype_C-AIOE_Percentile_75</t>
+          <t>Archetype_C-AIOE_Percentile_-_Observed_Exposure_75</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -32162,19 +32162,19 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>27-1013.00</t>
+          <t>41-1011.00</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Fine Artists, Including Painters, Sculptors, and Illustrators</t>
+          <t>First-Line Supervisors of Retail Sales Workers</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5.308549980919039</v>
+        <v>4.669897888258957</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.3565</v>
+        <v>0.2627</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -32182,11 +32182,11 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Sculptor Apprentice; Layout Artist; Motion Graphics Artist; Cartoonist; Painting Restorer; Picture Restorer; Visual Graphic Artist</t>
+          <t>Store Supervisor Trainee; Online Store Executive Assistant</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -32201,17 +32201,17 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>3</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
@@ -32222,19 +32222,19 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>41-2031.00</t>
+          <t>27-4021.00</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Retail Salespersons</t>
+          <t>Photographers</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>4.931678187819275</v>
+        <v>4.563433133726504</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.3222</v>
+        <v>0.195</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -32246,7 +32246,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Fashion Exhibition Assistant; Sales Assistant (High School)</t>
+          <t>Photographer; Professional Photographer</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -32261,17 +32261,17 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>3</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
@@ -32282,19 +32282,19 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>43-3031.00</t>
+          <t>19-4013.00</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Bookkeeping, Accounting, and Auditing Clerks</t>
+          <t>Food Science Technicians</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>5.634453631463048</v>
+        <v>4.693805289116916</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.3104</v>
+        <v>0.2038</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -32302,11 +32302,11 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Finance Associate; Cost Controller; Accounting Clerk (Healthcare); Accounting Staff (Construction); Finance Assistant (Cooperatives); Junior Airline Accounting Clerk; Site Accounting Assistant (Construction); Treasury Staff (Construction); Bookkeeper</t>
+          <t>Master Tagger</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -32321,17 +32321,17 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
@@ -32342,19 +32342,19 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>31-9094.00</t>
+          <t>15-1232.00</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Medical Transcriptionists</t>
+          <t>Computer User Support Specialists</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>5.229291282626066</v>
+        <v>4.631753405600366</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.6365</v>
+        <v>0.4685</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -32362,11 +32362,11 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Medical Transcriptionist</t>
+          <t>Enterprise Development Assistant; Interfaith Program Assistant; Database Assistant; Agricultural Data Assistant; M&amp;E Program Assistant; Technology Operations Assistant; Program Production Assistant; Technical Project Assistant; Computer Maintenance Technologist (Healthcare); IT Technical Support Personnel (Healthcare); LGU Program Assistant, Local Government Support Staff; MIS Technical Support (Healthcare); Programmable Logic Controller - Programming (Manufacturing); Cybersecurity Help Desk</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -32402,19 +32402,19 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>23-1021.00</t>
+          <t>29-2051.00</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Administrative Law Judges, Adjudicators, and Hearing Officers</t>
+          <t>Dietetic Technicians</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>5.422400874486133</v>
+        <v>4.393991510233755</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.3048</v>
+        <v>0.2446</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -32441,17 +32441,17 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>3</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
@@ -32462,19 +32462,19 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>23-1023.00</t>
+          <t>25-1121.00</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Judges, Magistrate Judges, and Magistrates</t>
+          <t>Art, Drama, and Music Teachers, Postsecondary</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4.363694493849052</v>
+        <v>4.619587243796251</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.3109</v>
+        <v>0.2142</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -32501,26 +32501,806 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>AI-Enabled Expansion</t>
+          <t>Limited Current Transformation</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>3</v>
       </c>
       <c r="M7" s="2" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>None identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>25-4012.00</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Curators</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>4.593849340484031</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.4123</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Local Heritage Specialist; Exhibits Specialist; Heritage Planner; Museum Curator; Museum Researcher</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>None identified</t>
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>29-1224.00</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Radiologists</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>4.475451489943528</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Limited Current Transformation</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>None identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>11-9151.00</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Social and Community Service Managers</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>4.667980347265192</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.1808</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Limited Current Transformation</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>None identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>25-1081.00</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Education Teachers, Postsecondary</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>4.666652117821552</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.2621</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Limited Current Transformation</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>None identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>25-2031.00</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Secondary School Teachers, Except Special and Career/Technical Education</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>4.572601199963038</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Religious Education Teacher; Livelihood Education Teacher; Science Subject Teacher; General Subject Basic Education Teacher; General Subject High School Teacher; Mathematics Teacher</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>None identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>29-9021.00</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Health Information Technologists and Medical Registrars</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>4.214580312503993</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Health Information Management Technician</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>None identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>41-1012.00</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>First-Line Supervisors of Non-Retail Sales Workers</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>4.497925536868533</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.2295</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Limited Current Transformation</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>None identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>25-1071.00</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Health Specialties Teachers, Postsecondary</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>4.3274725992322</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>None identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>25-2022.00</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Middle School Teachers, Except Special and Career/Technical Education</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>4.458502423409523</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>None identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>25-1052.00</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Chemistry Teachers, Postsecondary</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>4.446115097266733</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.2185</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Limited Current Transformation</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>None identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>25-1072.00</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Nursing Instructors and Teachers, Postsecondary</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>4.159553424263391</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.1909</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Limited Current Transformation</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>None identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>25-1042.00</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Biological Science Teachers, Postsecondary</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>4.241076441595916</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Anatomy and Physiology Instructor; Biology Instructor</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>None identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>23-1023.00</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Judges, Magistrate Judges, and Magistrates</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>4.363694493849052</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>AI-Enabled Expansion</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>None identified</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N7"/>
+  <autoFilter ref="A1:N20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -32601,11 +33381,11 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Flag</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -32643,11 +33423,11 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Flag</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -32792,12 +33572,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6 rows</t>
+          <t>19 rows</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Flag</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
